--- a/group_target/группы.xlsx
+++ b/group_target/группы.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://vk.com/club230032166</t>
+          <t>https://vk.com/miraculbooks</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -445,6 +445,1349 @@
         </is>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>https://vk.com/irene_12_13</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>https://vk.com/shevtsovanatali</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>https://vk.com/nika_smelaja_knigi</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>https://vk.com/laramorskayaromanidlyagenchin</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>https://vk.com/romanloves</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>https://vk.com/plohaya_dev</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>https://vk.com/novelist77</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>https://vk.com/sacrificialfire</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>https://vk.com/thefantasticworlds</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>https://vk.com/authorworlds</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>https://vk.com/public148103071</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>https://vk.com/litmarket_love</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>https://vk.com/public84554007</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>https://vk.com/allu_sant</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://vk.com/club227021846</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>https://vk.com/knigi_irina_romanova</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>https://vk.com/zhurnatal</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>https://vk.com/skvoz_stranizy</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>https://vk.com/public214181470</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>https://vk.com/public212939967</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://vk.com/viktoria_vinner</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://vk.com/public199614571</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://vk.com/book_maslova</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://vk.com/public222257829</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://vk.com/public201436024</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://vk.com/elena_tihay</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://vk.com/public214329728</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://vk.com/alena_jaga</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://vk.com/riskavolkova</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://vk.com/legendy_mirov</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://vk.com/public183484376</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://vk.com/knigaai</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://vk.com/public180847434</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://vk.com/clromantika</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://vk.com/mariarnobooks</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://vk.com/alya_moreyno</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://vk.com/alisabookoflove</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://vk.com/club205760528</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://vk.com/na_stranicah_knig</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://vk.com/club216905843</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://vk.com/club136827571</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://vk.com/booksscool</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://vk.com/ckazki_gusarova</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://vk.com/reklama_litnet</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://vk.com/club220568342</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://vk.com/alko_books</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://vk.com/lovelandbooks18</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://vk.com/public206169361</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://vk.com/skazochnici_18</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://vk.com/public202644011</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://vk.com/public176169219</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://vk.com/avtor_olga_sho</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://vk.com/public200725371</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://vk.com/logovoknigh</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://vk.com/club223655147</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://vk.com/readrus</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://vk.com/skazochniklight</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://vk.com/slr.books</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://vk.com/juliya_pozdno</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://vk.com/fantazy_knigi</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://vk.com/club206169361</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://vk.com/public198794011</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://vk.com/club204921654</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://vk.com/club216680442</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://vk.com/club203007218</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://vk.com/knizhnzamok</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://vk.com/literarybattleroyale</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://vk.com/club84554007</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://vk.com/public191496235</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>https://vk.com/bookroman18</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>https://vk.com/club213928815</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>https://vk.com/amazingworldsoffantasy</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>https://vk.com/public197810619</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>https://vk.com/public201718078</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>https://vk.com/public217112497</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>https://vk.com/territory_fantasy</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>https://vk.com/regina_mazur</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>https://vk.com/umnie_skazki_18</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Не удалось подписаться: [9] Flood control</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>https://vk.com/public211130050</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Ошибка: [9] Flood control</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
         <is>
           <t>Не удалось подписаться: [9] Flood control</t>
         </is>
